--- a/Raw Data/Stock and Production/MPOB Production 3Y.xlsx
+++ b/Raw Data/Stock and Production/MPOB Production 3Y.xlsx
@@ -1,42 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ClaudeCode\Raw Data\Stock and Production\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0AA2E9-3C92-41F3-B54D-7F20FFEDF99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="49560" yWindow="7635" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Table Data" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>MYPOMP-CPOTT (COMM_LAST)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="60" formatCode="dd/M/yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/m/yyyy;@"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -66,14 +84,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,328 +424,338 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="2" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>MYPOMP-CPOTT (COMM_LAST)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-      <c r="B2" t="str">
-        <v>Close</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="d">
-        <v>2026-01-01T00:00:00.000Z</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46054</v>
       </c>
       <c r="B3">
-        <v>1577454</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="d">
-        <v>2025-12-01T00:00:00.000Z</v>
+        <v>1284699</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46023</v>
       </c>
       <c r="B4">
+        <v>1577233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B5">
         <v>1829549</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="d">
-        <v>2025-11-01T00:00:00.000Z</v>
-      </c>
-      <c r="B5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B6">
         <v>1935510</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="d">
-        <v>2025-10-01T00:00:00.000Z</v>
-      </c>
-      <c r="B6">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B7">
         <v>2043886</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="d">
-        <v>2025-09-01T00:00:00.000Z</v>
-      </c>
-      <c r="B7">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B8">
         <v>1840983</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="d">
-        <v>2025-08-01T00:00:00.000Z</v>
-      </c>
-      <c r="B8">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B9">
         <v>1854766</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="d">
-        <v>2025-07-01T00:00:00.000Z</v>
-      </c>
-      <c r="B9">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B10">
         <v>1812417</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="d">
-        <v>2025-06-01T00:00:00.000Z</v>
-      </c>
-      <c r="B10">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B11">
         <v>1692370</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="d">
-        <v>2025-05-01T00:00:00.000Z</v>
-      </c>
-      <c r="B11">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B12">
         <v>1771621</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="d">
-        <v>2025-04-01T00:00:00.000Z</v>
-      </c>
-      <c r="B12">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>45748</v>
+      </c>
+      <c r="B13">
         <v>1686379</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="d">
-        <v>2025-03-01T00:00:00.000Z</v>
-      </c>
-      <c r="B13">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>45717</v>
+      </c>
+      <c r="B14">
         <v>1387431</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="d">
-        <v>2025-02-01T00:00:00.000Z</v>
-      </c>
-      <c r="B14">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>45689</v>
+      </c>
+      <c r="B15">
         <v>1188029</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="d">
-        <v>2025-01-01T00:00:00.000Z</v>
-      </c>
-      <c r="B15">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>45658</v>
+      </c>
+      <c r="B16">
         <v>1239545</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="d">
-        <v>2024-12-01T00:00:00.000Z</v>
-      </c>
-      <c r="B16">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>45627</v>
+      </c>
+      <c r="B17">
         <v>1486942</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="d">
-        <v>2024-11-01T00:00:00.000Z</v>
-      </c>
-      <c r="B17">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>45597</v>
+      </c>
+      <c r="B18">
         <v>1621294</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="d">
-        <v>2024-10-01T00:00:00.000Z</v>
-      </c>
-      <c r="B18">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>45566</v>
+      </c>
+      <c r="B19">
         <v>1797348</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="d">
-        <v>2024-09-01T00:00:00.000Z</v>
-      </c>
-      <c r="B19">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>45536</v>
+      </c>
+      <c r="B20">
         <v>1821933</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="d">
-        <v>2024-08-01T00:00:00.000Z</v>
-      </c>
-      <c r="B20">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>45505</v>
+      </c>
+      <c r="B21">
         <v>1893859</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="d">
-        <v>2024-07-01T00:00:00.000Z</v>
-      </c>
-      <c r="B21">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>45474</v>
+      </c>
+      <c r="B22">
         <v>1840999</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="d">
-        <v>2024-06-01T00:00:00.000Z</v>
-      </c>
-      <c r="B22">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>45444</v>
+      </c>
+      <c r="B23">
         <v>1615283</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="d">
-        <v>2024-05-01T00:00:00.000Z</v>
-      </c>
-      <c r="B23">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>45413</v>
+      </c>
+      <c r="B24">
         <v>1704495</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="d">
-        <v>2024-04-01T00:00:00.000Z</v>
-      </c>
-      <c r="B24">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>45383</v>
+      </c>
+      <c r="B25">
         <v>1501941</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="d">
-        <v>2024-03-01T00:00:00.000Z</v>
-      </c>
-      <c r="B25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>45352</v>
+      </c>
+      <c r="B26">
         <v>1392471</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="d">
-        <v>2024-02-01T00:00:00.000Z</v>
-      </c>
-      <c r="B26">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>45323</v>
+      </c>
+      <c r="B27">
         <v>1259572</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="d">
-        <v>2024-01-01T00:00:00.000Z</v>
-      </c>
-      <c r="B27">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>45292</v>
+      </c>
+      <c r="B28">
         <v>1402020</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="d">
-        <v>2023-12-01T00:00:00.000Z</v>
-      </c>
-      <c r="B28">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>45261</v>
+      </c>
+      <c r="B29">
         <v>1550797</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="d">
-        <v>2023-11-01T00:00:00.000Z</v>
-      </c>
-      <c r="B29">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>45231</v>
+      </c>
+      <c r="B30">
         <v>1788870</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="d">
-        <v>2023-10-01T00:00:00.000Z</v>
-      </c>
-      <c r="B30">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>45200</v>
+      </c>
+      <c r="B31">
         <v>1937224</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="d">
-        <v>2023-09-01T00:00:00.000Z</v>
-      </c>
-      <c r="B31">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>45170</v>
+      </c>
+      <c r="B32">
         <v>1829434</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="d">
-        <v>2023-08-01T00:00:00.000Z</v>
-      </c>
-      <c r="B32">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>45139</v>
+      </c>
+      <c r="B33">
         <v>1753472</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="d">
-        <v>2023-07-01T00:00:00.000Z</v>
-      </c>
-      <c r="B33">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>45108</v>
+      </c>
+      <c r="B34">
         <v>1609977</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="d">
-        <v>2023-06-01T00:00:00.000Z</v>
-      </c>
-      <c r="B34">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>45078</v>
+      </c>
+      <c r="B35">
         <v>1447795</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="d">
-        <v>2023-05-01T00:00:00.000Z</v>
-      </c>
-      <c r="B35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>45047</v>
+      </c>
+      <c r="B36">
         <v>1517546</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="d">
-        <v>2023-04-01T00:00:00.000Z</v>
-      </c>
-      <c r="B36">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>45017</v>
+      </c>
+      <c r="B37">
         <v>1196782</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="d">
-        <v>2023-03-01T00:00:00.000Z</v>
-      </c>
-      <c r="B37">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>44986</v>
+      </c>
+      <c r="B38">
         <v>1288354</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="d">
-        <v>2023-02-01T00:00:00.000Z</v>
-      </c>
-      <c r="B38">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>44958</v>
+      </c>
+      <c r="B39">
         <v>1253664</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="d">
-        <v>2023-01-01T00:00:00.000Z</v>
-      </c>
-      <c r="B39">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>44927</v>
+      </c>
+      <c r="B40">
         <v>1380410</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B39"/>
+    <ignoredError sqref="A5:B40 A1:B2 A4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Raw Data/Stock and Production/MPOB Production 3Y.xlsx
+++ b/Raw Data/Stock and Production/MPOB Production 3Y.xlsx
@@ -1,34 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ClaudeCode\Raw Data\Stock and Production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0AA2E9-3C92-41F3-B54D-7F20FFEDF99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE2970F-59EF-4B4F-82D7-F7A3348E3CBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="49560" yWindow="7635" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40080" yWindow="-20145" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -52,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/m/yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="dd/m/yyyy;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -85,7 +72,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -425,14 +412,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B124"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.875" customWidth="1"/>
     <col min="2" max="2" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -440,7 +427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -448,314 +435,986 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B3">
+        <v>1629801</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B4">
+        <v>1376849</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>46054</v>
       </c>
-      <c r="B3">
-        <v>1284699</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="B5">
+        <v>1284268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>46023</v>
       </c>
-      <c r="B4">
+      <c r="B6">
         <v>1577233</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>45992</v>
       </c>
-      <c r="B5">
+      <c r="B7">
         <v>1829549</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>45962</v>
       </c>
-      <c r="B6">
+      <c r="B8">
         <v>1935510</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>45931</v>
       </c>
-      <c r="B7">
+      <c r="B9">
         <v>2043886</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>45901</v>
       </c>
-      <c r="B8">
+      <c r="B10">
         <v>1840983</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>45870</v>
       </c>
-      <c r="B9">
+      <c r="B11">
         <v>1854766</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>45839</v>
       </c>
-      <c r="B10">
+      <c r="B12">
         <v>1812417</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>45809</v>
       </c>
-      <c r="B11">
+      <c r="B13">
         <v>1692370</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>45778</v>
       </c>
-      <c r="B12">
+      <c r="B14">
         <v>1771621</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>45748</v>
       </c>
-      <c r="B13">
+      <c r="B15">
         <v>1686379</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>45717</v>
       </c>
-      <c r="B14">
+      <c r="B16">
         <v>1387431</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>45689</v>
       </c>
-      <c r="B15">
+      <c r="B17">
         <v>1188029</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>45658</v>
       </c>
-      <c r="B16">
+      <c r="B18">
         <v>1239545</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>45627</v>
       </c>
-      <c r="B17">
+      <c r="B19">
         <v>1486942</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>45597</v>
       </c>
-      <c r="B18">
+      <c r="B20">
         <v>1621294</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>45566</v>
       </c>
-      <c r="B19">
+      <c r="B21">
         <v>1797348</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>45536</v>
       </c>
-      <c r="B20">
+      <c r="B22">
         <v>1821933</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>45505</v>
       </c>
-      <c r="B21">
+      <c r="B23">
         <v>1893859</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>45474</v>
       </c>
-      <c r="B22">
+      <c r="B24">
         <v>1840999</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>45444</v>
       </c>
-      <c r="B23">
+      <c r="B25">
         <v>1615283</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>45413</v>
       </c>
-      <c r="B24">
+      <c r="B26">
         <v>1704495</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>45383</v>
       </c>
-      <c r="B25">
+      <c r="B27">
         <v>1501941</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>45352</v>
       </c>
-      <c r="B26">
+      <c r="B28">
         <v>1392471</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>45323</v>
       </c>
-      <c r="B27">
+      <c r="B29">
         <v>1259572</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>45292</v>
       </c>
-      <c r="B28">
+      <c r="B30">
         <v>1402020</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>45261</v>
       </c>
-      <c r="B29">
+      <c r="B31">
         <v>1550797</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>45231</v>
       </c>
-      <c r="B30">
+      <c r="B32">
         <v>1788870</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>45200</v>
       </c>
-      <c r="B31">
+      <c r="B33">
         <v>1937224</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>45170</v>
       </c>
-      <c r="B32">
+      <c r="B34">
         <v>1829434</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>45139</v>
       </c>
-      <c r="B33">
+      <c r="B35">
         <v>1753472</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>45108</v>
       </c>
-      <c r="B34">
+      <c r="B36">
         <v>1609977</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>45078</v>
       </c>
-      <c r="B35">
+      <c r="B37">
         <v>1447795</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>45047</v>
       </c>
-      <c r="B36">
+      <c r="B38">
         <v>1517546</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>45017</v>
       </c>
-      <c r="B37">
+      <c r="B39">
         <v>1196782</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>44986</v>
       </c>
-      <c r="B38">
+      <c r="B40">
         <v>1288354</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>44958</v>
       </c>
-      <c r="B39">
+      <c r="B41">
         <v>1253664</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>44927</v>
       </c>
-      <c r="B40">
+      <c r="B42">
         <v>1380410</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>44896</v>
+      </c>
+      <c r="B43">
+        <v>1618833</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>44866</v>
+      </c>
+      <c r="B44">
+        <v>1680741</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>44835</v>
+      </c>
+      <c r="B45">
+        <v>1813591</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>44805</v>
+      </c>
+      <c r="B46">
+        <v>1770441</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>44774</v>
+      </c>
+      <c r="B47">
+        <v>1725781</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B48">
+        <v>1573560</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>44713</v>
+      </c>
+      <c r="B49">
+        <v>1545103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>44682</v>
+      </c>
+      <c r="B50">
+        <v>1461032</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>44652</v>
+      </c>
+      <c r="B51">
+        <v>1462021</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>44621</v>
+      </c>
+      <c r="B52">
+        <v>1411215</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>44593</v>
+      </c>
+      <c r="B53">
+        <v>1137460</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>44562</v>
+      </c>
+      <c r="B54">
+        <v>1253442</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>44531</v>
+      </c>
+      <c r="B55">
+        <v>1450905</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>44501</v>
+      </c>
+      <c r="B56">
+        <v>1634932</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>44470</v>
+      </c>
+      <c r="B57">
+        <v>1725837</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>44440</v>
+      </c>
+      <c r="B58">
+        <v>1703740</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>44409</v>
+      </c>
+      <c r="B59">
+        <v>1710356</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>44378</v>
+      </c>
+      <c r="B60">
+        <v>1523143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>44348</v>
+      </c>
+      <c r="B61">
+        <v>1606187</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>44317</v>
+      </c>
+      <c r="B62">
+        <v>1571523</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>44287</v>
+      </c>
+      <c r="B63">
+        <v>1522865</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>44256</v>
+      </c>
+      <c r="B64">
+        <v>1423483</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>44228</v>
+      </c>
+      <c r="B65">
+        <v>1108236</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>44197</v>
+      </c>
+      <c r="B66">
+        <v>1126457</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>44166</v>
+      </c>
+      <c r="B67">
+        <v>1333639</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>44136</v>
+      </c>
+      <c r="B68">
+        <v>1491551</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>44105</v>
+      </c>
+      <c r="B69">
+        <v>1724559</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>44075</v>
+      </c>
+      <c r="B70">
+        <v>1869255</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>44044</v>
+      </c>
+      <c r="B71">
+        <v>1863309</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>44013</v>
+      </c>
+      <c r="B72">
+        <v>1807397</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>43983</v>
+      </c>
+      <c r="B73">
+        <v>1885742</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>43952</v>
+      </c>
+      <c r="B74">
+        <v>1651336</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>43922</v>
+      </c>
+      <c r="B75">
+        <v>1652771</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>43891</v>
+      </c>
+      <c r="B76">
+        <v>1401481</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>43862</v>
+      </c>
+      <c r="B77">
+        <v>1288515</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>43831</v>
+      </c>
+      <c r="B78">
+        <v>1171534</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>43800</v>
+      </c>
+      <c r="B79">
+        <v>1333904</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>43770</v>
+      </c>
+      <c r="B80">
+        <v>1538053</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>43739</v>
+      </c>
+      <c r="B81">
+        <v>1795841</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>43709</v>
+      </c>
+      <c r="B82">
+        <v>1842433</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>43678</v>
+      </c>
+      <c r="B83">
+        <v>1821548</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>43647</v>
+      </c>
+      <c r="B84">
+        <v>1740759</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>43617</v>
+      </c>
+      <c r="B85">
+        <v>1510835</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>43586</v>
+      </c>
+      <c r="B86">
+        <v>1671467</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>43556</v>
+      </c>
+      <c r="B87">
+        <v>1649278</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>43525</v>
+      </c>
+      <c r="B88">
+        <v>1672058</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>43497</v>
+      </c>
+      <c r="B89">
+        <v>1544518</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>43466</v>
+      </c>
+      <c r="B90">
+        <v>1737461</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>43435</v>
+      </c>
+      <c r="B91">
+        <v>1808038</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>43405</v>
+      </c>
+      <c r="B92">
+        <v>1845222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>43374</v>
+      </c>
+      <c r="B93">
+        <v>1964954</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>43344</v>
+      </c>
+      <c r="B94">
+        <v>1853602</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>43313</v>
+      </c>
+      <c r="B95">
+        <v>1622231</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>43282</v>
+      </c>
+      <c r="B96">
+        <v>1503220</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>43252</v>
+      </c>
+      <c r="B97">
+        <v>1332705</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>43221</v>
+      </c>
+      <c r="B98">
+        <v>1525405</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>43191</v>
+      </c>
+      <c r="B99">
+        <v>1558331</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>43160</v>
+      </c>
+      <c r="B100">
+        <v>1573957</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>43132</v>
+      </c>
+      <c r="B101">
+        <v>1342805</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>43101</v>
+      </c>
+      <c r="B102">
+        <v>1586646</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>43070</v>
+      </c>
+      <c r="B103">
+        <v>1834165</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>43040</v>
+      </c>
+      <c r="B104">
+        <v>1942847</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>43009</v>
+      </c>
+      <c r="B105">
+        <v>2008838</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B106">
+        <v>1779918</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>42948</v>
+      </c>
+      <c r="B107">
+        <v>1810594</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>42917</v>
+      </c>
+      <c r="B108">
+        <v>1827108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>42887</v>
+      </c>
+      <c r="B109">
+        <v>1514165</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>42856</v>
+      </c>
+      <c r="B110">
+        <v>1654494</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>42826</v>
+      </c>
+      <c r="B111">
+        <v>1548053</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>42795</v>
+      </c>
+      <c r="B112">
+        <v>1464021</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>42767</v>
+      </c>
+      <c r="B113">
+        <v>1258539</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>42736</v>
+      </c>
+      <c r="B114">
+        <v>1276852</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>42705</v>
+      </c>
+      <c r="B115">
+        <v>1473717</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>42675</v>
+      </c>
+      <c r="B116">
+        <v>1574938</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>42644</v>
+      </c>
+      <c r="B117">
+        <v>1677873</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>42614</v>
+      </c>
+      <c r="B118">
+        <v>1715085</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>42583</v>
+      </c>
+      <c r="B119">
+        <v>1701831</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>42552</v>
+      </c>
+      <c r="B120">
+        <v>1585882</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>42522</v>
+      </c>
+      <c r="B121">
+        <v>1532613</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>42491</v>
+      </c>
+      <c r="B122">
+        <v>1364575</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>42461</v>
+      </c>
+      <c r="B123">
+        <v>1301291</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>42430</v>
+      </c>
+      <c r="B124">
+        <v>1219483</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A5:B40 A1:B2 A4" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:B124 A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Raw Data/Stock and Production/MPOB Production 3Y.xlsx
+++ b/Raw Data/Stock and Production/MPOB Production 3Y.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ClaudeCode\Raw Data\Stock and Production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE2970F-59EF-4B4F-82D7-F7A3348E3CBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF16FA4-734A-4B55-895E-84E0E40AE09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40080" yWindow="-20145" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table Data" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/m/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd/m/yyyy;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -72,7 +72,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,14 +412,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B124"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B125"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.875" customWidth="1"/>
     <col min="2" max="2" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -427,7 +427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -435,986 +435,994 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B3">
+        <v>1516327</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>46113</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>1629801</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>46082</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>1376849</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>46054</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>1284268</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>46023</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>1577233</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>45992</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>1829549</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>45962</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>1935510</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>45931</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>2043886</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>45901</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>1840983</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>45870</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>1854766</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>45839</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>1812417</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>45809</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>1692370</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>45778</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>1771621</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>45748</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>1686379</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>45717</v>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>1387431</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>45689</v>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>1188029</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>45658</v>
       </c>
-      <c r="B18">
+      <c r="B19">
         <v>1239545</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>45627</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>1486942</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>45597</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>1621294</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>45566</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>1797348</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>45536</v>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>1821933</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>45505</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>1893859</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>45474</v>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>1840999</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>45444</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <v>1615283</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>45413</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>1704495</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>45383</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>1501941</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>45352</v>
       </c>
-      <c r="B28">
+      <c r="B29">
         <v>1392471</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>45323</v>
       </c>
-      <c r="B29">
+      <c r="B30">
         <v>1259572</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>45292</v>
       </c>
-      <c r="B30">
+      <c r="B31">
         <v>1402020</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>45261</v>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>1550797</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>45231</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>1788870</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>45200</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>1937224</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>45170</v>
       </c>
-      <c r="B34">
+      <c r="B35">
         <v>1829434</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>45139</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>1753472</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>45108</v>
       </c>
-      <c r="B36">
+      <c r="B37">
         <v>1609977</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>45078</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>1447795</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>45047</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>1517546</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>45017</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>1196782</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>44986</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>1288354</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>44958</v>
       </c>
-      <c r="B41">
+      <c r="B42">
         <v>1253664</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>44927</v>
       </c>
-      <c r="B42">
+      <c r="B43">
         <v>1380410</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>44896</v>
       </c>
-      <c r="B43">
+      <c r="B44">
         <v>1618833</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>44866</v>
       </c>
-      <c r="B44">
+      <c r="B45">
         <v>1680741</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>44835</v>
       </c>
-      <c r="B45">
+      <c r="B46">
         <v>1813591</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>44805</v>
       </c>
-      <c r="B46">
+      <c r="B47">
         <v>1770441</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>44774</v>
       </c>
-      <c r="B47">
+      <c r="B48">
         <v>1725781</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>44743</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>1573560</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>44713</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>1545103</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>44682</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>1461032</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>44652</v>
       </c>
-      <c r="B51">
+      <c r="B52">
         <v>1462021</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>44621</v>
       </c>
-      <c r="B52">
+      <c r="B53">
         <v>1411215</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>44593</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>1137460</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>44562</v>
       </c>
-      <c r="B54">
+      <c r="B55">
         <v>1253442</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>44531</v>
       </c>
-      <c r="B55">
+      <c r="B56">
         <v>1450905</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>44501</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>1634932</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>44470</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <v>1725837</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>44440</v>
       </c>
-      <c r="B58">
+      <c r="B59">
         <v>1703740</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>44409</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <v>1710356</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>44378</v>
       </c>
-      <c r="B60">
+      <c r="B61">
         <v>1523143</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>44348</v>
       </c>
-      <c r="B61">
+      <c r="B62">
         <v>1606187</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>44317</v>
       </c>
-      <c r="B62">
+      <c r="B63">
         <v>1571523</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>44287</v>
       </c>
-      <c r="B63">
+      <c r="B64">
         <v>1522865</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>44256</v>
       </c>
-      <c r="B64">
+      <c r="B65">
         <v>1423483</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>44228</v>
       </c>
-      <c r="B65">
+      <c r="B66">
         <v>1108236</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>44197</v>
       </c>
-      <c r="B66">
+      <c r="B67">
         <v>1126457</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>44166</v>
       </c>
-      <c r="B67">
+      <c r="B68">
         <v>1333639</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>44136</v>
       </c>
-      <c r="B68">
+      <c r="B69">
         <v>1491551</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
         <v>44105</v>
       </c>
-      <c r="B69">
+      <c r="B70">
         <v>1724559</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>44075</v>
       </c>
-      <c r="B70">
+      <c r="B71">
         <v>1869255</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
         <v>44044</v>
       </c>
-      <c r="B71">
+      <c r="B72">
         <v>1863309</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>44013</v>
       </c>
-      <c r="B72">
+      <c r="B73">
         <v>1807397</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
         <v>43983</v>
       </c>
-      <c r="B73">
+      <c r="B74">
         <v>1885742</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
         <v>43952</v>
       </c>
-      <c r="B74">
+      <c r="B75">
         <v>1651336</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
         <v>43922</v>
       </c>
-      <c r="B75">
+      <c r="B76">
         <v>1652771</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
         <v>43891</v>
       </c>
-      <c r="B76">
+      <c r="B77">
         <v>1401481</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
         <v>43862</v>
       </c>
-      <c r="B77">
+      <c r="B78">
         <v>1288515</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>43831</v>
       </c>
-      <c r="B78">
+      <c r="B79">
         <v>1171534</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
         <v>43800</v>
       </c>
-      <c r="B79">
+      <c r="B80">
         <v>1333904</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
         <v>43770</v>
       </c>
-      <c r="B80">
+      <c r="B81">
         <v>1538053</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
         <v>43739</v>
       </c>
-      <c r="B81">
+      <c r="B82">
         <v>1795841</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
         <v>43709</v>
       </c>
-      <c r="B82">
+      <c r="B83">
         <v>1842433</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
         <v>43678</v>
       </c>
-      <c r="B83">
+      <c r="B84">
         <v>1821548</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
         <v>43647</v>
       </c>
-      <c r="B84">
+      <c r="B85">
         <v>1740759</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
         <v>43617</v>
       </c>
-      <c r="B85">
+      <c r="B86">
         <v>1510835</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
         <v>43586</v>
       </c>
-      <c r="B86">
+      <c r="B87">
         <v>1671467</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
         <v>43556</v>
       </c>
-      <c r="B87">
+      <c r="B88">
         <v>1649278</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
         <v>43525</v>
       </c>
-      <c r="B88">
+      <c r="B89">
         <v>1672058</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
         <v>43497</v>
       </c>
-      <c r="B89">
+      <c r="B90">
         <v>1544518</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
         <v>43466</v>
       </c>
-      <c r="B90">
+      <c r="B91">
         <v>1737461</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
         <v>43435</v>
       </c>
-      <c r="B91">
+      <c r="B92">
         <v>1808038</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
         <v>43405</v>
       </c>
-      <c r="B92">
+      <c r="B93">
         <v>1845222</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
         <v>43374</v>
       </c>
-      <c r="B93">
+      <c r="B94">
         <v>1964954</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
         <v>43344</v>
       </c>
-      <c r="B94">
+      <c r="B95">
         <v>1853602</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
         <v>43313</v>
       </c>
-      <c r="B95">
+      <c r="B96">
         <v>1622231</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
         <v>43282</v>
       </c>
-      <c r="B96">
+      <c r="B97">
         <v>1503220</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
         <v>43252</v>
       </c>
-      <c r="B97">
+      <c r="B98">
         <v>1332705</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
         <v>43221</v>
       </c>
-      <c r="B98">
+      <c r="B99">
         <v>1525405</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
         <v>43191</v>
       </c>
-      <c r="B99">
+      <c r="B100">
         <v>1558331</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
         <v>43160</v>
       </c>
-      <c r="B100">
+      <c r="B101">
         <v>1573957</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
         <v>43132</v>
       </c>
-      <c r="B101">
+      <c r="B102">
         <v>1342805</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
         <v>43101</v>
       </c>
-      <c r="B102">
+      <c r="B103">
         <v>1586646</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
         <v>43070</v>
       </c>
-      <c r="B103">
+      <c r="B104">
         <v>1834165</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="1">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
         <v>43040</v>
       </c>
-      <c r="B104">
+      <c r="B105">
         <v>1942847</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="1">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
         <v>43009</v>
       </c>
-      <c r="B105">
+      <c r="B106">
         <v>2008838</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
         <v>42979</v>
       </c>
-      <c r="B106">
+      <c r="B107">
         <v>1779918</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
         <v>42948</v>
       </c>
-      <c r="B107">
+      <c r="B108">
         <v>1810594</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
         <v>42917</v>
       </c>
-      <c r="B108">
+      <c r="B109">
         <v>1827108</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="1">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
         <v>42887</v>
       </c>
-      <c r="B109">
+      <c r="B110">
         <v>1514165</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
         <v>42856</v>
       </c>
-      <c r="B110">
+      <c r="B111">
         <v>1654494</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
         <v>42826</v>
       </c>
-      <c r="B111">
+      <c r="B112">
         <v>1548053</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
         <v>42795</v>
       </c>
-      <c r="B112">
+      <c r="B113">
         <v>1464021</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
         <v>42767</v>
       </c>
-      <c r="B113">
+      <c r="B114">
         <v>1258539</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
         <v>42736</v>
       </c>
-      <c r="B114">
+      <c r="B115">
         <v>1276852</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
         <v>42705</v>
       </c>
-      <c r="B115">
+      <c r="B116">
         <v>1473717</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
         <v>42675</v>
       </c>
-      <c r="B116">
+      <c r="B117">
         <v>1574938</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
         <v>42644</v>
       </c>
-      <c r="B117">
+      <c r="B118">
         <v>1677873</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
         <v>42614</v>
       </c>
-      <c r="B118">
+      <c r="B119">
         <v>1715085</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
         <v>42583</v>
       </c>
-      <c r="B119">
+      <c r="B120">
         <v>1701831</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
         <v>42552</v>
       </c>
-      <c r="B120">
+      <c r="B121">
         <v>1585882</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
         <v>42522</v>
       </c>
-      <c r="B121">
+      <c r="B122">
         <v>1532613</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="1">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
         <v>42491</v>
       </c>
-      <c r="B122">
+      <c r="B123">
         <v>1364575</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>42461</v>
       </c>
-      <c r="B123">
+      <c r="B124">
         <v>1301291</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
         <v>42430</v>
       </c>
-      <c r="B124">
+      <c r="B125">
         <v>1219483</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A4:B124 A1:B2" numberStoredAsText="1"/>
+    <ignoredError sqref="A5:B125 A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>